--- a/ctl-site/src/assets/PAGINA_INICIAL/NOTICIAS.xlsx
+++ b/ctl-site/src/assets/PAGINA_INICIAL/NOTICIAS.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\ctl-angular\ctl-angular\src\assets\PAGINA_INICIAL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9be54d10f24db4ff/CTL site/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B09D9AAD-84DD-431A-BC34-AE3A4BDC95BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{74B7AB77-2888-441B-9D56-AAB5C07C2704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -29,7 +40,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="3">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -44,45 +55,20 @@
         </ext>
       </extLst>
     </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2"/>
-        </ext>
-      </extLst>
-    </bk>
   </futureMetadata>
-  <valueMetadata count="3">
+  <valueMetadata count="2">
     <bk>
       <rc t="1" v="0"/>
     </bk>
     <bk>
       <rc t="1" v="1"/>
     </bk>
-    <bk>
-      <rc t="1" v="2"/>
-    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
-  <si>
-    <t>Lorem ipsum dolor sit amet, consectetur adipiscing elit, sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum.</t>
-  </si>
-  <si>
-    <t>Texto pequeno para testar notícias com menos texto.</t>
-  </si>
-  <si>
-    <t>Título muito lindo</t>
-  </si>
-  <si>
-    <t>Mais um título, ainda mais lindo</t>
-  </si>
-  <si>
-    <t>Este título é excepcionalmente longo. À partida não haverá títulos assim, mas é só para testar todos os casos</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t xml:space="preserve">DESCRIÇÃO
 (OBRIGATÓRIA) </t>
@@ -97,6 +83,19 @@
 Nota: O sistema aceita qualquer tamanho/rácio de foto. 
 No início é mostrado  um quadrado com o conteúdo central da foto.
 Na modal é exibida a foto completa.</t>
+  </si>
+  <si>
+    <t>Consignação IRS 2026</t>
+  </si>
+  <si>
+    <t>Inscrições Interrupção Letiva da Páscoa 2026</t>
+  </si>
+  <si>
+    <t>Encontram-se  abertas as inscrições para a Interrupção Letiva do Carnaval. As Atividades destinam-se a crianças entre os 6 e os 10 anos de idade. Os interessados têm até ao dia 20 de março para efetuar a inscrição. Para mais informações: 239 445 810 ou ctlsc@outlook.com</t>
+  </si>
+  <si>
+    <t>A consignação do IRS é uma forma simples e sem custos de apoiar a nossa instituição. Ao preencher a sua declaração de IRS, pode destinar 1% do imposto já liquidado pelo Estado à nossa instituição. Este gesto não aumenta o valor do seu imposto nem diminui o eventual reembolso, apenas direciona uma pequena parte do imposto para uma causa solidária.
+Consigne 1% do seu IRS à nossa instituição e ajude-nos a continuar a transformar vidas.                                       Ao preencher a sua declaração de IRS, não se esqueça de assinalar: Modelo 3 Quadro 11 Campo 1101 (IPSS) NIPC 502 389 818</t>
   </si>
 </sst>
 </file>
@@ -221,7 +220,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -230,10 +229,6 @@
     <v>1</v>
     <v>5</v>
   </rv>
-  <rv s="0">
-    <v>2</v>
-    <v>5</v>
-  </rv>
 </rvData>
 </file>
 
@@ -250,7 +245,6 @@
 <richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <rel r:id="rId1"/>
   <rel r:id="rId2"/>
-  <rel r:id="rId3"/>
 </richValueRels>
 </file>
 
@@ -518,58 +512,48 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="49.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="61.21875" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="40.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="49.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="61.28515625" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="171" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="135" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>0</v>
       </c>
       <c r="C2" s="1" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="133.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="133.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="1" t="e" vm="3">
-        <v>#VALUE!</v>
-      </c>
-    </row>
+    <row r="4" spans="1:3" ht="130.9" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
